--- a/research/traditional_assets/database/data/germany/germany_retail_automotive.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_retail_automotive.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.01493341378270051</v>
+        <v>-0.02579862018100521</v>
       </c>
       <c r="H2">
-        <v>-0.01493341378270051</v>
+        <v>-0.02579862018100521</v>
       </c>
       <c r="I2">
-        <v>-0.03417661509287592</v>
+        <v>-0.03346598853736114</v>
       </c>
       <c r="J2">
-        <v>-0.03417661509287592</v>
+        <v>-0.03346598853736114</v>
       </c>
       <c r="K2">
-        <v>-437.7</v>
+        <v>-240.7</v>
       </c>
       <c r="L2">
-        <v>-0.09431970003878808</v>
+        <v>-0.03698468062875493</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,70 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>274.9</v>
+        <v>273</v>
       </c>
       <c r="V2">
-        <v>0.05978686385384949</v>
+        <v>0.1536556537400799</v>
       </c>
       <c r="W2">
-        <v>-6.243937232524964</v>
+        <v>-0.2011028490266522</v>
       </c>
       <c r="X2">
-        <v>0.05132088611832816</v>
+        <v>0.09239518561034635</v>
       </c>
       <c r="Y2">
-        <v>-6.295258118643293</v>
+        <v>-0.2934980346369985</v>
       </c>
       <c r="Z2">
-        <v>24.25823314166231</v>
+        <v>6.544750603378921</v>
       </c>
       <c r="AA2">
-        <v>-0.8290642969158389</v>
+        <v>-0.2190265486725664</v>
       </c>
       <c r="AB2">
-        <v>0.05048655525417125</v>
+        <v>0.07805044247404169</v>
       </c>
       <c r="AC2">
-        <v>-0.8795508521700102</v>
+        <v>-0.297076991146608</v>
       </c>
       <c r="AD2">
-        <v>133.3</v>
+        <v>644.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>133.3</v>
+        <v>644.4</v>
       </c>
       <c r="AG2">
-        <v>-141.6</v>
+        <v>371.4</v>
       </c>
       <c r="AH2">
-        <v>0.02817407477860208</v>
+        <v>0.2661600099128495</v>
       </c>
       <c r="AI2">
-        <v>0.1054004902348383</v>
+        <v>0.4707429322813937</v>
       </c>
       <c r="AJ2">
-        <v>-0.03177452652365137</v>
+        <v>0.1728969787253852</v>
       </c>
       <c r="AK2">
-        <v>-0.1430592038795716</v>
+        <v>0.338899534629072</v>
       </c>
       <c r="AL2">
-        <v>249.7</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>249.672</v>
+        <v>-189.3</v>
       </c>
       <c r="AN2">
-        <v>-0.8684039087947883</v>
-      </c>
-      <c r="AO2">
-        <v>-0.6351621946335603</v>
+        <v>-2.784788245462403</v>
       </c>
       <c r="AP2">
-        <v>0.9224755700325731</v>
+        <v>-1.605012964563526</v>
       </c>
       <c r="AQ2">
-        <v>-0.6352334262552468</v>
+        <v>1.150554675118859</v>
       </c>
     </row>
     <row r="3">
@@ -713,22 +710,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.01493341378270051</v>
+        <v>-0.02579862018100521</v>
       </c>
       <c r="H3">
-        <v>-0.01493341378270051</v>
+        <v>-0.02579862018100521</v>
       </c>
       <c r="I3">
-        <v>-0.03417661509287592</v>
+        <v>-0.03346598853736114</v>
       </c>
       <c r="J3">
-        <v>-0.03417661509287592</v>
+        <v>-0.03346598853736114</v>
       </c>
       <c r="K3">
-        <v>-437.7</v>
+        <v>-240.7</v>
       </c>
       <c r="L3">
-        <v>-0.09431970003878808</v>
+        <v>-0.03698468062875493</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +749,70 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>274.9</v>
+        <v>273</v>
       </c>
       <c r="V3">
-        <v>0.05978686385384949</v>
+        <v>0.1536556537400799</v>
       </c>
       <c r="W3">
-        <v>-6.243937232524964</v>
+        <v>-0.2011028490266522</v>
       </c>
       <c r="X3">
-        <v>0.05132088611832816</v>
+        <v>0.09239518561034635</v>
       </c>
       <c r="Y3">
-        <v>-6.295258118643293</v>
+        <v>-0.2934980346369985</v>
       </c>
       <c r="Z3">
-        <v>24.25823314166231</v>
+        <v>6.544750603378921</v>
       </c>
       <c r="AA3">
-        <v>-0.8290642969158389</v>
+        <v>-0.2190265486725664</v>
       </c>
       <c r="AB3">
-        <v>0.05048655525417125</v>
+        <v>0.07805044247404169</v>
       </c>
       <c r="AC3">
-        <v>-0.8795508521700102</v>
+        <v>-0.297076991146608</v>
       </c>
       <c r="AD3">
-        <v>133.3</v>
+        <v>644.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>133.3</v>
+        <v>644.4</v>
       </c>
       <c r="AG3">
-        <v>-141.6</v>
+        <v>371.4</v>
       </c>
       <c r="AH3">
-        <v>0.02817407477860208</v>
+        <v>0.2661600099128495</v>
       </c>
       <c r="AI3">
-        <v>0.1054004902348383</v>
+        <v>0.4707429322813937</v>
       </c>
       <c r="AJ3">
-        <v>-0.03177452652365137</v>
+        <v>0.1728969787253852</v>
       </c>
       <c r="AK3">
-        <v>-0.1430592038795716</v>
+        <v>0.338899534629072</v>
       </c>
       <c r="AL3">
-        <v>249.7</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>249.672</v>
+        <v>-189.3</v>
       </c>
       <c r="AN3">
-        <v>-0.8684039087947883</v>
-      </c>
-      <c r="AO3">
-        <v>-0.6351621946335603</v>
+        <v>-2.784788245462403</v>
       </c>
       <c r="AP3">
-        <v>0.9224755700325731</v>
+        <v>-1.605012964563526</v>
       </c>
       <c r="AQ3">
-        <v>-0.6352334262552468</v>
+        <v>1.150554675118859</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/germany/germany_retail_automotive.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_retail_automotive.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,23 +587,29 @@
           <t>Retail (Automotive)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>-0.0592</v>
+      </c>
+      <c r="E2">
+        <v>-0.106</v>
+      </c>
       <c r="G2">
-        <v>-0.02579862018100521</v>
+        <v>-0.03518953558738188</v>
       </c>
       <c r="H2">
-        <v>-0.02579862018100521</v>
+        <v>-0.03518953558738188</v>
       </c>
       <c r="I2">
-        <v>-0.03346598853736114</v>
+        <v>-0.02339596878054836</v>
       </c>
       <c r="J2">
-        <v>-0.03346598853736114</v>
+        <v>-0.02339596878054836</v>
       </c>
       <c r="K2">
-        <v>-240.7</v>
+        <v>-159.54</v>
       </c>
       <c r="L2">
-        <v>-0.03698468062875493</v>
+        <v>-0.02475522522382733</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,70 +633,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>273</v>
+        <v>579.3000000000001</v>
       </c>
       <c r="V2">
-        <v>0.1536556537400799</v>
+        <v>0.365442846328539</v>
       </c>
       <c r="W2">
-        <v>-0.2011028490266522</v>
+        <v>-0.09120082815734988</v>
       </c>
       <c r="X2">
-        <v>0.09239518561034635</v>
+        <v>0.106256400886242</v>
       </c>
       <c r="Y2">
-        <v>-0.2934980346369985</v>
+        <v>-0.1974572290435919</v>
       </c>
       <c r="Z2">
-        <v>6.544750603378921</v>
+        <v>5.338950054261831</v>
       </c>
       <c r="AA2">
-        <v>-0.2190265486725664</v>
+        <v>-0.08285111194918264</v>
       </c>
       <c r="AB2">
-        <v>0.07805044247404169</v>
+        <v>0.06482184995667839</v>
       </c>
       <c r="AC2">
-        <v>-0.297076991146608</v>
+        <v>-0.147672961905861</v>
       </c>
       <c r="AD2">
-        <v>644.4</v>
+        <v>768.9000000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>644.4</v>
+        <v>768.9000000000001</v>
       </c>
       <c r="AG2">
-        <v>371.4</v>
+        <v>189.6</v>
       </c>
       <c r="AH2">
-        <v>0.2661600099128495</v>
+        <v>0.3266216388428699</v>
       </c>
       <c r="AI2">
-        <v>0.4707429322813937</v>
+        <v>0.5297643654402646</v>
       </c>
       <c r="AJ2">
-        <v>0.1728969787253852</v>
+        <v>0.1068289384719405</v>
       </c>
       <c r="AK2">
-        <v>0.338899534629072</v>
+        <v>0.217406260749914</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>9.93</v>
       </c>
       <c r="AM2">
-        <v>-189.3</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="AN2">
-        <v>-2.784788245462403</v>
+        <v>-5.537231744202796</v>
+      </c>
+      <c r="AO2">
+        <v>-15.18429003021148</v>
       </c>
       <c r="AP2">
-        <v>-1.605012964563526</v>
+        <v>-1.365404004032839</v>
       </c>
       <c r="AQ2">
-        <v>1.150554675118859</v>
+        <v>-16.99887260428411</v>
       </c>
     </row>
     <row r="3">
@@ -701,118 +710,252 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Delticom AG (XTRA:DEX)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Retail (Automotive)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>-0.0592</v>
+      </c>
+      <c r="E3">
+        <v>-0.106</v>
+      </c>
+      <c r="G3">
+        <v>-0.0005376950554615529</v>
+      </c>
+      <c r="H3">
+        <v>-0.0005376950554615529</v>
+      </c>
+      <c r="I3">
+        <v>-0.006542583192329385</v>
+      </c>
+      <c r="J3">
+        <v>-0.006542583192329385</v>
+      </c>
+      <c r="K3">
+        <v>1.66</v>
+      </c>
+      <c r="L3">
+        <v>0.003120887384846776</v>
+      </c>
+      <c r="M3">
+        <v>-0</v>
+      </c>
+      <c r="N3">
+        <v>-0</v>
+      </c>
+      <c r="O3">
+        <v>-0</v>
+      </c>
+      <c r="P3">
+        <v>-0</v>
+      </c>
+      <c r="Q3">
+        <v>-0</v>
+      </c>
+      <c r="R3">
+        <v>-0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>2.7</v>
+      </c>
+      <c r="V3">
+        <v>0.07458563535911603</v>
+      </c>
+      <c r="W3">
+        <v>0.04009661835748792</v>
+      </c>
+      <c r="X3">
+        <v>0.1310495346258443</v>
+      </c>
+      <c r="Y3">
+        <v>-0.09095291626835636</v>
+      </c>
+      <c r="Z3">
+        <v>4.782843269490153</v>
+      </c>
+      <c r="AA3">
+        <v>-0.03129214998651201</v>
+      </c>
+      <c r="AB3">
+        <v>0.06209640991913776</v>
+      </c>
+      <c r="AC3">
+        <v>-0.09338855990564976</v>
+      </c>
+      <c r="AD3">
+        <v>94.2</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>94.2</v>
+      </c>
+      <c r="AG3">
+        <v>91.5</v>
+      </c>
+      <c r="AH3">
+        <v>0.7223926380368098</v>
+      </c>
+      <c r="AI3">
+        <v>0.6762383345297918</v>
+      </c>
+      <c r="AJ3">
+        <v>0.716523101018011</v>
+      </c>
+      <c r="AK3">
+        <v>0.6698389458272328</v>
+      </c>
+      <c r="AL3">
+        <v>2.75</v>
+      </c>
+      <c r="AM3">
+        <v>2.75</v>
+      </c>
+      <c r="AN3">
+        <v>-34.1304347826087</v>
+      </c>
+      <c r="AO3">
+        <v>-1.265454545454545</v>
+      </c>
+      <c r="AP3">
+        <v>-33.15217391304348</v>
+      </c>
+      <c r="AQ3">
+        <v>-1.265454545454545</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>AUTO1 Group SE (XTRA:AG1)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Retail (Automotive)</t>
         </is>
       </c>
-      <c r="G3">
-        <v>-0.02579862018100521</v>
-      </c>
-      <c r="H3">
-        <v>-0.02579862018100521</v>
-      </c>
-      <c r="I3">
-        <v>-0.03346598853736114</v>
-      </c>
-      <c r="J3">
-        <v>-0.03346598853736114</v>
-      </c>
-      <c r="K3">
-        <v>-240.7</v>
-      </c>
-      <c r="L3">
-        <v>-0.03698468062875493</v>
-      </c>
-      <c r="M3">
-        <v>-0</v>
-      </c>
-      <c r="N3">
-        <v>-0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>-0</v>
-      </c>
-      <c r="Q3">
-        <v>-0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>273</v>
-      </c>
-      <c r="V3">
-        <v>0.1536556537400799</v>
-      </c>
-      <c r="W3">
-        <v>-0.2011028490266522</v>
-      </c>
-      <c r="X3">
-        <v>0.09239518561034635</v>
-      </c>
-      <c r="Y3">
-        <v>-0.2934980346369985</v>
-      </c>
-      <c r="Z3">
-        <v>6.544750603378921</v>
-      </c>
-      <c r="AA3">
-        <v>-0.2190265486725664</v>
-      </c>
-      <c r="AB3">
-        <v>0.07805044247404169</v>
-      </c>
-      <c r="AC3">
-        <v>-0.297076991146608</v>
-      </c>
-      <c r="AD3">
-        <v>644.4</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>644.4</v>
-      </c>
-      <c r="AG3">
-        <v>371.4</v>
-      </c>
-      <c r="AH3">
-        <v>0.2661600099128495</v>
-      </c>
-      <c r="AI3">
-        <v>0.4707429322813937</v>
-      </c>
-      <c r="AJ3">
-        <v>0.1728969787253852</v>
-      </c>
-      <c r="AK3">
-        <v>0.338899534629072</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>-189.3</v>
-      </c>
-      <c r="AN3">
-        <v>-2.784788245462403</v>
-      </c>
-      <c r="AP3">
-        <v>-1.605012964563526</v>
-      </c>
-      <c r="AQ3">
-        <v>1.150554675118859</v>
+      <c r="G4">
+        <v>-0.03830672439453389</v>
+      </c>
+      <c r="H4">
+        <v>-0.03830672439453389</v>
+      </c>
+      <c r="I4">
+        <v>-0.02491205520227304</v>
+      </c>
+      <c r="J4">
+        <v>-0.02491205520227304</v>
+      </c>
+      <c r="K4">
+        <v>-161.2</v>
+      </c>
+      <c r="L4">
+        <v>-0.02726288729535922</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>576.6</v>
+      </c>
+      <c r="V4">
+        <v>0.3722401549386701</v>
+      </c>
+      <c r="W4">
+        <v>-0.2224982746721877</v>
+      </c>
+      <c r="X4">
+        <v>0.08146326714663968</v>
+      </c>
+      <c r="Y4">
+        <v>-0.3039615418188274</v>
+      </c>
+      <c r="Z4">
+        <v>5.395382790400584</v>
+      </c>
+      <c r="AA4">
+        <v>-0.1344100739118533</v>
+      </c>
+      <c r="AB4">
+        <v>0.06754728999421902</v>
+      </c>
+      <c r="AC4">
+        <v>-0.2019573639060723</v>
+      </c>
+      <c r="AD4">
+        <v>674.7</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>674.7</v>
+      </c>
+      <c r="AG4">
+        <v>98.10000000000002</v>
+      </c>
+      <c r="AH4">
+        <v>0.3034132302019158</v>
+      </c>
+      <c r="AI4">
+        <v>0.5142138556512461</v>
+      </c>
+      <c r="AJ4">
+        <v>0.05955922530508168</v>
+      </c>
+      <c r="AK4">
+        <v>0.1333786539768865</v>
+      </c>
+      <c r="AL4">
+        <v>7.18</v>
+      </c>
+      <c r="AM4">
+        <v>6.119999999999999</v>
+      </c>
+      <c r="AN4">
+        <v>-4.957384276267451</v>
+      </c>
+      <c r="AO4">
+        <v>-20.51532033426184</v>
+      </c>
+      <c r="AP4">
+        <v>-0.7207935341660545</v>
+      </c>
+      <c r="AQ4">
+        <v>-24.0686274509804</v>
       </c>
     </row>
   </sheetData>
